--- a/result1.xlsx
+++ b/result1.xlsx
@@ -1008,7 +1008,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>911.16138333333333</v>
+        <v>577.82804999999996</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" ht="14" customHeight="true" x14ac:dyDescent="0.25">
@@ -2088,7 +2088,7 @@
         <v>150</v>
       </c>
       <c r="B145" s="2">
-        <v>574.12098333333324</v>
+        <v>907.4543166666665</v>
       </c>
     </row>
   </sheetData>
@@ -2153,7 +2153,7 @@
         <v>833.33333333333326</v>
       </c>
       <c r="C3" s="5">
-        <v>6365.8411999999998</v>
+        <v>5947.41975</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>156</v>
@@ -2167,10 +2167,10 @@
         <v>146</v>
       </c>
       <c r="B4" s="5">
-        <v>4787.9642880658485</v>
+        <v>3954.6309547325154</v>
       </c>
       <c r="C4" s="5">
-        <v>1702.9969833333334</v>
+        <v>2121.4184333333333</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" s="5" customFormat="true" ht="14" customHeight="true" x14ac:dyDescent="0.35">
@@ -2178,7 +2178,7 @@
         <v>147</v>
       </c>
       <c r="B5" s="5">
-        <v>5286.0351769547315</v>
+        <v>6119.3685102880636</v>
       </c>
       <c r="C5" s="5">
         <v>91.101383333333501</v>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="5">
-        <v>5780.1318833333335</v>
+        <v>5068.68685</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" s="5" customFormat="true" ht="14" customHeight="true" x14ac:dyDescent="0.35">
@@ -2203,7 +2203,7 @@
         <v>5333.3333333333321</v>
       </c>
       <c r="C7" s="5">
-        <v>2859.8681166666665</v>
+        <v>3571.31315</v>
       </c>
     </row>
   </sheetData>
